--- a/output/roomself_excel/1019.xlsx
+++ b/output/roomself_excel/1019.xlsx
@@ -498,10 +498,10 @@
         <v>5932</v>
       </c>
       <c r="E3" t="n">
-        <v>1091</v>
+        <v>1039</v>
       </c>
       <c r="F3" t="n">
-        <v>1039</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4">
@@ -608,10 +608,10 @@
         <v>3088</v>
       </c>
       <c r="E8" t="n">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="F8" t="n">
-        <v>336</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">

--- a/output/roomself_excel/1019.xlsx
+++ b/output/roomself_excel/1019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2396</v>
       </c>
-      <c r="E2" t="n">
-        <v>356</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>270</v>
+        <v>236</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>315</v>
+      </c>
+      <c r="J2" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>5932</v>
       </c>
-      <c r="E3" t="n">
-        <v>1039</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>414</v>
+        <v>396</v>
+      </c>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>373</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2932</v>
       </c>
-      <c r="E4" t="n">
-        <v>404</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>394</v>
+        <v>360</v>
+      </c>
+      <c r="G4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>373</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +609,20 @@
       <c r="D5" t="n">
         <v>1488</v>
       </c>
-      <c r="E5" t="n">
-        <v>190</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +639,12 @@
       <c r="D6" t="n">
         <v>1188</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +661,20 @@
       <c r="D7" t="n">
         <v>1464</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>159</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>34</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>3088</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>412</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>34</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +721,27 @@
       <c r="D9" t="n">
         <v>2680</v>
       </c>
-      <c r="E9" t="n">
-        <v>440</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>297</v>
+        <v>395</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>264</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>680</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>55</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>34</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +789,27 @@
       <c r="D11" t="n">
         <v>1856</v>
       </c>
-      <c r="E11" t="n">
-        <v>329</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>177</v>
+        <v>354</v>
+      </c>
+      <c r="G11" t="n">
+        <v>21</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>287</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
